--- a/Results/Ethylene/ethylene climate change image breakdown results.xlsx
+++ b/Results/Ethylene/ethylene climate change image breakdown results.xlsx
@@ -496,22 +496,22 @@
         <v>2.153785412491858</v>
       </c>
       <c r="E2" t="n">
-        <v>1.923773824168965</v>
+        <v>1.923773824168967</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413198</v>
+        <v>0.1005026380413199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729404</v>
+        <v>0.007350774813729365</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417118e-05</v>
+        <v>6.571721692417115e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965752</v>
+        <v>0.001092413434965748</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000448159536</v>
+        <v>0.1210000448159518</v>
       </c>
     </row>
     <row r="3">
@@ -529,22 +529,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.136999103341148</v>
+        <v>2.136999103341147</v>
       </c>
       <c r="E3" t="n">
         <v>1.911197437544212</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066853</v>
+        <v>0.09636540113066852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967805</v>
+        <v>0.007312726439967746</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915012e-05</v>
+        <v>6.385850907915017e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837414</v>
+        <v>0.001059635361837415</v>
       </c>
       <c r="J3" t="n">
         <v>0.121000044355382</v>
@@ -565,25 +565,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.126798813103924</v>
+        <v>2.126798813103925</v>
       </c>
       <c r="E4" t="n">
         <v>1.903144226251773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0942728560206398</v>
+        <v>0.09427285602063984</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682902</v>
+        <v>0.007288038605682941</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418662e-05</v>
+        <v>6.399694265418645e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001029651197070435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000440861032</v>
+        <v>0.121000044086105</v>
       </c>
     </row>
     <row r="5">
@@ -601,25 +601,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.106126687815304</v>
+        <v>2.106126687815308</v>
       </c>
       <c r="E5" t="n">
-        <v>1.888954340445296</v>
+        <v>1.888954340445298</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765819</v>
+        <v>0.08786371902765827</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.46575616480839e-05</v>
+        <v>6.465756164808396e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374646</v>
+        <v>0.0009969273959374641</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000434852037</v>
+        <v>0.1210000434852057</v>
       </c>
     </row>
     <row r="6">
@@ -637,25 +637,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.927256878018745</v>
+        <v>1.927256878018743</v>
       </c>
       <c r="E6" t="n">
-        <v>1.769287934305169</v>
+        <v>1.769287934305167</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431356</v>
+        <v>0.02921941151431359</v>
       </c>
       <c r="G6" t="n">
         <v>0.006913950708356127</v>
       </c>
       <c r="H6" t="n">
-        <v>5.30242537707515e-05</v>
+        <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971275</v>
+        <v>0.0007825190314971271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000382056378</v>
+        <v>0.1210000382056382</v>
       </c>
     </row>
     <row r="7">
@@ -676,22 +676,22 @@
         <v>1.802967037481159</v>
       </c>
       <c r="E7" t="n">
-        <v>1.684162283819533</v>
+        <v>1.684162283819534</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799131</v>
+        <v>-0.009541766337799044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752118</v>
+        <v>0.006680214285752079</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289982e-05</v>
+        <v>4.620437260289991e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006200667534924644</v>
+        <v>0.000620066753492464</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000345875775</v>
+        <v>0.1210000345875777</v>
       </c>
     </row>
     <row r="8">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.776603657634233</v>
+        <v>1.776603657634229</v>
       </c>
       <c r="E8" t="n">
-        <v>1.665115357805203</v>
+        <v>1.6651153578052</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178214</v>
+        <v>-0.01676581279178204</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006629040989846969</v>
+        <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.46991863391496e-05</v>
+        <v>4.469918633914963e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747333</v>
+        <v>0.0005803385990747337</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000338455515</v>
+        <v>0.1210000338455501</v>
       </c>
     </row>
     <row r="9">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.083403481835335</v>
+        <v>2.083403481835336</v>
       </c>
       <c r="E9" t="n">
-        <v>1.874259015620756</v>
+        <v>1.874259015620759</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736006</v>
+        <v>0.0798909042736005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294439</v>
+        <v>0.007212354243294438</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791409e-05</v>
+        <v>6.116855081791398e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750915</v>
+        <v>0.0009799963456750874</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000428011908</v>
+        <v>0.1210000428011897</v>
       </c>
     </row>
     <row r="10">
@@ -787,19 +787,19 @@
         <v>1.761941414741507</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0261847535430475</v>
+        <v>0.02618475354304766</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699897</v>
+        <v>0.006898886718699891</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931318e-05</v>
+        <v>5.252414845931317e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801691</v>
+        <v>0.0007668618399801689</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000379078007</v>
+        <v>0.1210000379078005</v>
       </c>
     </row>
     <row r="11">
@@ -817,25 +817,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.815874957428775</v>
+        <v>1.815874957428774</v>
       </c>
       <c r="E11" t="n">
-        <v>1.694434199177175</v>
+        <v>1.694434199177176</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.006960801978537628</v>
+        <v>-0.00696080197853775</v>
       </c>
       <c r="G11" t="n">
         <v>0.006709262029071818</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740453e-05</v>
+        <v>4.717660518740441e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199603</v>
+        <v>0.0006450866694199601</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000349264593</v>
+        <v>0.1210000349264568</v>
       </c>
     </row>
   </sheetData>
@@ -917,22 +917,22 @@
         <v>1.431016168624998</v>
       </c>
       <c r="E2" t="n">
-        <v>1.201004595625669</v>
+        <v>1.201004595625668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413198</v>
+        <v>0.1005026380413199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729404</v>
+        <v>0.007350774813729365</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417118e-05</v>
+        <v>6.571721692417115e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965752</v>
+        <v>0.001092413434965748</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000294923903</v>
+        <v>0.1210000294923907</v>
       </c>
     </row>
     <row r="3">
@@ -953,22 +953,22 @@
         <v>1.405245458631877</v>
       </c>
       <c r="E3" t="n">
-        <v>1.179443808348987</v>
+        <v>1.179443808348989</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066853</v>
+        <v>0.09636540113066852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967805</v>
+        <v>0.007312726439967746</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915012e-05</v>
+        <v>6.385850907915017e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837414</v>
+        <v>0.001059635361837415</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000288413375</v>
+        <v>0.1210000288413355</v>
       </c>
     </row>
     <row r="4">
@@ -992,19 +992,19 @@
         <v>1.166979602723256</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0942728560206398</v>
+        <v>0.09427285602063984</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682902</v>
+        <v>0.007288038605682941</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418662e-05</v>
+        <v>6.399694265418645e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001029651197070435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000284785491</v>
+        <v>0.1210000284785484</v>
       </c>
     </row>
     <row r="5">
@@ -1022,25 +1022,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.354681902465523</v>
+        <v>1.354681902465526</v>
       </c>
       <c r="E5" t="n">
-        <v>1.137509571027031</v>
+        <v>1.13750957102703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765819</v>
+        <v>0.08786371902765827</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.46575616480839e-05</v>
+        <v>6.465756164808396e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374646</v>
+        <v>0.0009969273959374641</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000275536884</v>
+        <v>0.121000027553692</v>
       </c>
     </row>
     <row r="6">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.032101447109946</v>
+        <v>1.032101447109944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8741325223747187</v>
+        <v>0.8741325223747191</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431356</v>
+        <v>0.02921941151431359</v>
       </c>
       <c r="G6" t="n">
         <v>0.006913950708356127</v>
       </c>
       <c r="H6" t="n">
-        <v>5.30242537707515e-05</v>
+        <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971275</v>
+        <v>0.0007825190314971271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000192272899</v>
+        <v>0.1210000192272874</v>
       </c>
     </row>
     <row r="7">
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8144874503369421</v>
+        <v>0.8144874503369428</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6956827176322434</v>
+        <v>0.695682717632246</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799131</v>
+        <v>-0.009541766337799044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752118</v>
+        <v>0.006680214285752079</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289982e-05</v>
+        <v>4.620437260289991e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006200667534924644</v>
+        <v>0.000620066753492464</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000136306503</v>
+        <v>0.1210000136306484</v>
       </c>
     </row>
     <row r="8">
@@ -1130,25 +1130,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7716585005350776</v>
+        <v>0.7716585005350795</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6601702220120649</v>
+        <v>0.6601702220120641</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178214</v>
+        <v>-0.01676581279178204</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006629040989846969</v>
+        <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.46991863391496e-05</v>
+        <v>4.469918633914963e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747333</v>
+        <v>0.0005803385990747337</v>
       </c>
       <c r="J8" t="n">
-        <v>0.121000012539534</v>
+        <v>0.1210000125395365</v>
       </c>
     </row>
     <row r="9">
@@ -1166,25 +1166,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.311990680701729</v>
+        <v>1.31199068070173</v>
       </c>
       <c r="E9" t="n">
-        <v>1.102846230842002</v>
+        <v>1.102846230842003</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736006</v>
+        <v>0.0798909042736005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294439</v>
+        <v>0.007212354243294438</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791409e-05</v>
+        <v>6.116855081791398e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750915</v>
+        <v>0.0009799963456750874</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000264463391</v>
+        <v>0.1210000264463389</v>
       </c>
     </row>
     <row r="10">
@@ -1205,22 +1205,22 @@
         <v>1.014546361397182</v>
       </c>
       <c r="E10" t="n">
-        <v>0.859643316368975</v>
+        <v>0.8596433163689733</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0261847535430475</v>
+        <v>0.02618475354304766</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699897</v>
+        <v>0.006898886718699891</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931318e-05</v>
+        <v>5.252414845931317e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801691</v>
+        <v>0.0007668618399801689</v>
       </c>
       <c r="J10" t="n">
-        <v>0.12100001877802</v>
+        <v>0.1210000187780214</v>
       </c>
     </row>
     <row r="11">
@@ -1238,25 +1238,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8317108467883249</v>
+        <v>0.8317108467883234</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7102701094021504</v>
+        <v>0.7102701094021497</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.006960801978537628</v>
+        <v>-0.00696080197853775</v>
       </c>
       <c r="G11" t="n">
         <v>0.006709262029071818</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740453e-05</v>
+        <v>4.717660518740441e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199603</v>
+        <v>0.0006450866694199601</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000140610329</v>
+        <v>0.1210000140610322</v>
       </c>
     </row>
   </sheetData>
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.865385302258377</v>
+        <v>-1.865385302258364</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.095396805370267</v>
+        <v>-2.095396805370108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413198</v>
+        <v>0.1005026380413199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729404</v>
+        <v>0.007350774813729365</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417118e-05</v>
+        <v>6.571721692417115e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965752</v>
+        <v>0.001092413434965748</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999596049502</v>
+        <v>0.1209999596048039</v>
       </c>
     </row>
     <row r="3">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.015928670874358</v>
+        <v>-2.015928670874374</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.241730248624367</v>
+        <v>-2.241730248624355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066853</v>
+        <v>0.09636540113066852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967805</v>
+        <v>0.007312726439967746</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915012e-05</v>
+        <v>6.385850907915017e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837414</v>
+        <v>0.001059635361837415</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999563084554</v>
+        <v>0.120999956308427</v>
       </c>
     </row>
     <row r="4">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.125456230626132</v>
+        <v>-2.125456230626126</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.349110727325462</v>
+        <v>-2.349110727325464</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0942728560206398</v>
+        <v>0.09427285602063984</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682902</v>
+        <v>0.007288038605682941</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418662e-05</v>
+        <v>6.399694265418645e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001029651197070435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.120999953933282</v>
+        <v>0.1209999539332909</v>
       </c>
     </row>
     <row r="5">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.203597524652159</v>
+        <v>-2.203597524652155</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.420769780650912</v>
+        <v>-2.420769780650947</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765819</v>
+        <v>0.08786371902765827</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.46575616480839e-05</v>
+        <v>6.465756164808396e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374646</v>
+        <v>0.0009969273959374641</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999521139489</v>
+        <v>0.1209999521139866</v>
       </c>
     </row>
     <row r="6">
@@ -1479,25 +1479,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.900967072018712</v>
+        <v>-2.900967072018864</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.058935913368358</v>
+        <v>-3.058935913368399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431356</v>
+        <v>0.02921941151431359</v>
       </c>
       <c r="G6" t="n">
         <v>0.006913950708356127</v>
       </c>
       <c r="H6" t="n">
-        <v>5.30242537707515e-05</v>
+        <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971275</v>
+        <v>0.0007825190314971271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999358417084</v>
+        <v>0.1209999358415974</v>
       </c>
     </row>
     <row r="7">
@@ -1515,25 +1515,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.433445380976878</v>
+        <v>-3.433445380976883</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.552250023620435</v>
+        <v>-3.55225002362041</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799131</v>
+        <v>-0.009541766337799044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752118</v>
+        <v>0.006680214285752079</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289982e-05</v>
+        <v>4.620437260289991e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006200667534924644</v>
+        <v>0.000620066753492464</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999235695087</v>
+        <v>0.1209999235694781</v>
       </c>
     </row>
     <row r="8">
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.549789716013567</v>
+        <v>-3.549789716013659</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.661277902916806</v>
+        <v>-3.661277902916882</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178214</v>
+        <v>-0.01676581279178204</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006629040989846969</v>
+        <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.46991863391496e-05</v>
+        <v>4.469918633914963e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747333</v>
+        <v>0.0005803385990747337</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999209197603</v>
+        <v>0.1209999209197448</v>
       </c>
     </row>
     <row r="9">
@@ -1587,25 +1587,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.263700982267238</v>
+        <v>-2.263700982267203</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.472845356318107</v>
+        <v>-2.472845356318112</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736006</v>
+        <v>0.0798909042736005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294439</v>
+        <v>0.007212354243294438</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791409e-05</v>
+        <v>6.116855081791398e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750915</v>
+        <v>0.0009799963456750874</v>
       </c>
       <c r="J9" t="n">
-        <v>0.120999950637481</v>
+        <v>0.1209999506375214</v>
       </c>
     </row>
     <row r="10">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.975674700511219</v>
+        <v>-2.975674700511282</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.130577660942081</v>
+        <v>-3.130577660942113</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0261847535430475</v>
+        <v>0.02618475354304766</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699897</v>
+        <v>0.006898886718699891</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931318e-05</v>
+        <v>5.252414845931317e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801691</v>
+        <v>0.0007668618399801689</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999341806758</v>
+        <v>0.1209999341806438</v>
       </c>
     </row>
     <row r="11">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.369108114860806</v>
+        <v>-3.369108114860852</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.490548763184709</v>
+        <v>-3.490548763184747</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.006960801978537628</v>
+        <v>-0.00696080197853775</v>
       </c>
       <c r="G11" t="n">
         <v>0.006709262029071818</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740453e-05</v>
+        <v>4.717660518740441e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199603</v>
+        <v>0.0006450866694199601</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999249987614</v>
+        <v>0.1209999249987539</v>
       </c>
     </row>
   </sheetData>
@@ -1756,25 +1756,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.294689107118041</v>
+        <v>-1.294689107117994</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.52470062232927</v>
+        <v>-1.52470062232917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413198</v>
+        <v>0.1005026380413199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729404</v>
+        <v>0.007350774813729365</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417118e-05</v>
+        <v>6.571721692417115e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965752</v>
+        <v>0.001092413434965748</v>
       </c>
       <c r="J2" t="n">
-        <v>0.12099997170429</v>
+        <v>0.1209999717042369</v>
       </c>
     </row>
     <row r="3">
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.59428553304265</v>
+        <v>-1.594285533042652</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.820087119731959</v>
+        <v>-1.820087119731961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066853</v>
+        <v>0.09636540113066852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967805</v>
+        <v>0.007312726439967746</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915012e-05</v>
+        <v>6.385850907915017e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837414</v>
+        <v>0.001059635361837415</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999652477567</v>
+        <v>0.1209999652477565</v>
       </c>
     </row>
     <row r="4">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.781553520690106</v>
+        <v>-1.781553520690094</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.005208024680543</v>
+        <v>-2.005208024680584</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0942728560206398</v>
+        <v>0.09427285602063984</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682902</v>
+        <v>0.007288038605682941</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418662e-05</v>
+        <v>6.399694265418645e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001029651197070435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999612243902</v>
+        <v>0.1209999612244426</v>
       </c>
     </row>
     <row r="5">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.89912328244307</v>
+        <v>-1.899123282443093</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.116295544896987</v>
+        <v>-2.116295544897085</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765819</v>
+        <v>0.08786371902765827</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.46575616480839e-05</v>
+        <v>6.465756164808396e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374646</v>
+        <v>0.0009969273959374641</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999585691122</v>
+        <v>0.1209999585691874</v>
       </c>
     </row>
     <row r="6">
@@ -1900,25 +1900,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.625527686213402</v>
+        <v>-2.625527686213487</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.783496533402595</v>
+        <v>-2.783496533402669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431356</v>
+        <v>0.02921941151431359</v>
       </c>
       <c r="G6" t="n">
         <v>0.006913950708356127</v>
       </c>
       <c r="H6" t="n">
-        <v>5.30242537707515e-05</v>
+        <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971275</v>
+        <v>0.0007825190314971271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999416812555</v>
+        <v>0.1209999416812444</v>
       </c>
     </row>
     <row r="7">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.275962258504332</v>
+        <v>-3.275962258504333</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.394766904486693</v>
+        <v>-3.394766904486695</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799131</v>
+        <v>-0.009541766337799044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752118</v>
+        <v>0.006680214285752079</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289982e-05</v>
+        <v>4.620437260289991e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006200667534924644</v>
+        <v>0.000620066753492464</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999269083122</v>
+        <v>0.1209999269083131</v>
       </c>
     </row>
     <row r="8">
@@ -1972,25 +1972,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.413354992402362</v>
+        <v>-3.413354992402458</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.524843182198233</v>
+        <v>-3.524843182198278</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178214</v>
+        <v>-0.01676581279178204</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006629040989846969</v>
+        <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.46991863391496e-05</v>
+        <v>4.469918633914963e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747333</v>
+        <v>0.0005803385990747337</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999238123922</v>
+        <v>0.1209999238123411</v>
       </c>
     </row>
     <row r="9">
@@ -2008,25 +2008,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.869044331379936</v>
+        <v>-1.869044331379985</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.078188713797972</v>
+        <v>-2.078188713798014</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736006</v>
+        <v>0.0798909042736005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294439</v>
+        <v>0.007212354243294438</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791409e-05</v>
+        <v>6.116855081791398e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750915</v>
+        <v>0.0009799963456750874</v>
       </c>
       <c r="J9" t="n">
-        <v>0.120999959004648</v>
+        <v>0.1209999590046402</v>
       </c>
     </row>
     <row r="10">
@@ -2044,25 +2044,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.755477427594886</v>
+        <v>-2.755477427594946</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.910380392694148</v>
+        <v>-2.910380392694229</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0261847535430475</v>
+        <v>0.02618475354304766</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699897</v>
+        <v>0.006898886718699891</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931318e-05</v>
+        <v>5.252414845931317e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801691</v>
+        <v>0.0007668618399801689</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999388490748</v>
+        <v>0.1209999388490952</v>
       </c>
     </row>
     <row r="11">
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.228818386639053</v>
+        <v>-3.228818386639041</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.35025903793723</v>
+        <v>-3.3502590379372</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.006960801978537628</v>
+        <v>-0.00696080197853775</v>
       </c>
       <c r="G11" t="n">
         <v>0.006709262029071818</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740453e-05</v>
+        <v>4.717660518740441e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199603</v>
+        <v>0.0006450866694199601</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999279730356</v>
+        <v>0.1209999279730183</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ethylene/ethylene climate change image breakdown results.xlsx
+++ b/Results/Ethylene/ethylene climate change image breakdown results.xlsx
@@ -499,16 +499,16 @@
         <v>1.923773824168967</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413199</v>
+        <v>0.1005026380413198</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729365</v>
+        <v>0.007350774813729363</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417115e-05</v>
+        <v>6.571721692417118e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965748</v>
+        <v>0.001092413434965749</v>
       </c>
       <c r="J2" t="n">
         <v>0.1210000448159518</v>
@@ -529,25 +529,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.136999103341147</v>
+        <v>2.136999103341148</v>
       </c>
       <c r="E3" t="n">
-        <v>1.911197437544212</v>
+        <v>1.911197437544214</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066852</v>
+        <v>0.09636540113066856</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967746</v>
+        <v>0.007312726439967809</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915017e-05</v>
+        <v>6.385850907915014e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837415</v>
+        <v>0.001059635361837416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.121000044355382</v>
+        <v>0.1210000443553803</v>
       </c>
     </row>
     <row r="4">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.126798813103925</v>
+        <v>2.126798813103926</v>
       </c>
       <c r="E4" t="n">
-        <v>1.903144226251773</v>
+        <v>1.903144226251774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09427285602063984</v>
+        <v>0.09427285602063995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682941</v>
+        <v>0.007288038605682944</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418645e-05</v>
+        <v>6.399694265418654e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001029651197070435</v>
+        <v>0.001029651197070432</v>
       </c>
       <c r="J4" t="n">
         <v>0.121000044086105</v>
@@ -604,22 +604,22 @@
         <v>2.106126687815308</v>
       </c>
       <c r="E5" t="n">
-        <v>1.888954340445298</v>
+        <v>1.8889543404453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765827</v>
+        <v>0.08786371902765802</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.465756164808396e-05</v>
+        <v>6.4657561648084e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374641</v>
+        <v>0.0009969273959374665</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000434852057</v>
+        <v>0.1210000434852032</v>
       </c>
     </row>
     <row r="6">
@@ -640,22 +640,22 @@
         <v>1.927256878018743</v>
       </c>
       <c r="E6" t="n">
-        <v>1.769287934305167</v>
+        <v>1.769287934305168</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431359</v>
+        <v>0.02921941151431353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006913950708356127</v>
+        <v>0.006913950708356131</v>
       </c>
       <c r="H6" t="n">
         <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971271</v>
+        <v>0.0007825190314971269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000382056382</v>
+        <v>0.1210000382056371</v>
       </c>
     </row>
     <row r="7">
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.802967037481159</v>
+        <v>1.802967037481157</v>
       </c>
       <c r="E7" t="n">
-        <v>1.684162283819534</v>
+        <v>1.684162283819532</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799044</v>
+        <v>-0.009541766337799015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752079</v>
+        <v>0.006680214285752085</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289991e-05</v>
+        <v>4.620437260289981e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000620066753492464</v>
+        <v>0.0006200667534924634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000345875777</v>
+        <v>0.1210000345875775</v>
       </c>
     </row>
     <row r="8">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.776603657634229</v>
+        <v>1.776603657634231</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6651153578052</v>
+        <v>1.665115357805203</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178204</v>
+        <v>-0.01676581279178216</v>
       </c>
       <c r="G8" t="n">
         <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.469918633914963e-05</v>
+        <v>4.469918633914951e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747337</v>
+        <v>0.0005803385990747353</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000338455501</v>
+        <v>0.1210000338455497</v>
       </c>
     </row>
     <row r="9">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.083403481835336</v>
+        <v>2.083403481835335</v>
       </c>
       <c r="E9" t="n">
-        <v>1.874259015620759</v>
+        <v>1.874259015620755</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736005</v>
+        <v>0.07989090427360057</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294438</v>
+        <v>0.00721235424329444</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791398e-05</v>
+        <v>6.116855081791406e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750874</v>
+        <v>0.0009799963456750887</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000428011897</v>
+        <v>0.1210000428011915</v>
       </c>
     </row>
     <row r="10">
@@ -784,22 +784,22 @@
         <v>1.916844478899495</v>
       </c>
       <c r="E10" t="n">
-        <v>1.761941414741507</v>
+        <v>1.761941414741509</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02618475354304766</v>
+        <v>0.02618475354304757</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699891</v>
+        <v>0.006898886718699889</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931317e-05</v>
+        <v>5.252414845931323e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801689</v>
+        <v>0.0007668618399801692</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000379078005</v>
+        <v>0.1210000379077993</v>
       </c>
     </row>
     <row r="11">
@@ -817,25 +817,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.815874957428774</v>
+        <v>1.815874957428776</v>
       </c>
       <c r="E11" t="n">
-        <v>1.694434199177176</v>
+        <v>1.694434199177177</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.00696080197853775</v>
+        <v>-0.006960801978537704</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006709262029071818</v>
+        <v>0.006709262029071785</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740441e-05</v>
+        <v>4.717660518740447e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199601</v>
+        <v>0.0006450866694199596</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000349264568</v>
+        <v>0.1210000349264566</v>
       </c>
     </row>
   </sheetData>
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.431016168624998</v>
+        <v>1.431016168624997</v>
       </c>
       <c r="E2" t="n">
         <v>1.201004595625668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413199</v>
+        <v>0.1005026380413198</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729365</v>
+        <v>0.007350774813729363</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417115e-05</v>
+        <v>6.571721692417118e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965748</v>
+        <v>0.001092413434965749</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000294923907</v>
+        <v>0.1210000294923901</v>
       </c>
     </row>
     <row r="3">
@@ -950,25 +950,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.405245458631877</v>
+        <v>1.405245458631876</v>
       </c>
       <c r="E3" t="n">
-        <v>1.179443808348989</v>
+        <v>1.179443808348988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066852</v>
+        <v>0.09636540113066856</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967746</v>
+        <v>0.007312726439967809</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915017e-05</v>
+        <v>6.385850907915014e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837415</v>
+        <v>0.001059635361837416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000288413355</v>
+        <v>0.1210000288413358</v>
       </c>
     </row>
     <row r="4">
@@ -992,19 +992,19 @@
         <v>1.166979602723256</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09427285602063984</v>
+        <v>0.09427285602063995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682941</v>
+        <v>0.007288038605682944</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418645e-05</v>
+        <v>6.399694265418654e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001029651197070435</v>
+        <v>0.001029651197070432</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000284785484</v>
+        <v>0.1210000284785486</v>
       </c>
     </row>
     <row r="5">
@@ -1022,25 +1022,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.354681902465526</v>
+        <v>1.354681902465527</v>
       </c>
       <c r="E5" t="n">
-        <v>1.13750957102703</v>
+        <v>1.137509571027034</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765827</v>
+        <v>0.08786371902765802</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.465756164808396e-05</v>
+        <v>6.4657561648084e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374641</v>
+        <v>0.0009969273959374665</v>
       </c>
       <c r="J5" t="n">
-        <v>0.121000027553692</v>
+        <v>0.1210000275536882</v>
       </c>
     </row>
     <row r="6">
@@ -1061,22 +1061,22 @@
         <v>1.032101447109944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8741325223747191</v>
+        <v>0.8741325223747186</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431359</v>
+        <v>0.02921941151431353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006913950708356127</v>
+        <v>0.006913950708356131</v>
       </c>
       <c r="H6" t="n">
         <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971271</v>
+        <v>0.0007825190314971269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000192272874</v>
+        <v>0.1210000192272875</v>
       </c>
     </row>
     <row r="7">
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8144874503369428</v>
+        <v>0.8144874503369406</v>
       </c>
       <c r="E7" t="n">
-        <v>0.695682717632246</v>
+        <v>0.6956827176322434</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799044</v>
+        <v>-0.009541766337799015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752079</v>
+        <v>0.006680214285752085</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289991e-05</v>
+        <v>4.620437260289981e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000620066753492464</v>
+        <v>0.0006200667534924634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000136306484</v>
+        <v>0.1210000136306487</v>
       </c>
     </row>
     <row r="8">
@@ -1133,22 +1133,22 @@
         <v>0.7716585005350795</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6601702220120641</v>
+        <v>0.6601702220120661</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178204</v>
+        <v>-0.01676581279178216</v>
       </c>
       <c r="G8" t="n">
         <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.469918633914963e-05</v>
+        <v>4.469918633914951e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747337</v>
+        <v>0.0005803385990747353</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000125395365</v>
+        <v>0.1210000125395346</v>
       </c>
     </row>
     <row r="9">
@@ -1166,22 +1166,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.31199068070173</v>
+        <v>1.311990680701729</v>
       </c>
       <c r="E9" t="n">
-        <v>1.102846230842003</v>
+        <v>1.102846230842002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736005</v>
+        <v>0.07989090427360057</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294438</v>
+        <v>0.00721235424329444</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791398e-05</v>
+        <v>6.116855081791406e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750874</v>
+        <v>0.0009799963456750887</v>
       </c>
       <c r="J9" t="n">
         <v>0.1210000264463389</v>
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.014546361397182</v>
+        <v>1.014546361397181</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8596433163689733</v>
+        <v>0.8596433163689737</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02618475354304766</v>
+        <v>0.02618475354304757</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699891</v>
+        <v>0.006898886718699889</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931317e-05</v>
+        <v>5.252414845931323e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801689</v>
+        <v>0.0007668618399801692</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000187780214</v>
+        <v>0.1210000187780202</v>
       </c>
     </row>
     <row r="11">
@@ -1241,22 +1241,22 @@
         <v>0.8317108467883234</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7102701094021497</v>
+        <v>0.7102701094021494</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.00696080197853775</v>
+        <v>-0.006960801978537704</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006709262029071818</v>
+        <v>0.006709262029071785</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740441e-05</v>
+        <v>4.717660518740447e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199601</v>
+        <v>0.0006450866694199596</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1210000140610322</v>
+        <v>0.1210000140610326</v>
       </c>
     </row>
   </sheetData>
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.865385302258364</v>
+        <v>-1.86538530225835</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.095396805370108</v>
+        <v>-2.095396805370107</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413199</v>
+        <v>0.1005026380413198</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729365</v>
+        <v>0.007350774813729363</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417115e-05</v>
+        <v>6.571721692417118e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965748</v>
+        <v>0.001092413434965749</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999596048039</v>
+        <v>0.1209999596048179</v>
       </c>
     </row>
     <row r="3">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.015928670874374</v>
+        <v>-2.015928670874412</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.241730248624355</v>
+        <v>-2.241730248624344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066852</v>
+        <v>0.09636540113066856</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967746</v>
+        <v>0.007312726439967809</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915017e-05</v>
+        <v>6.385850907915014e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837415</v>
+        <v>0.001059635361837416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.120999956308427</v>
+        <v>0.120999956308379</v>
       </c>
     </row>
     <row r="4">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.125456230626126</v>
+        <v>-2.125456230626138</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.349110727325464</v>
+        <v>-2.34911072732552</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09427285602063984</v>
+        <v>0.09427285602063995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682941</v>
+        <v>0.007288038605682944</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418645e-05</v>
+        <v>6.399694265418654e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001029651197070435</v>
+        <v>0.001029651197070432</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999539332909</v>
+        <v>0.1209999539333344</v>
       </c>
     </row>
     <row r="5">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.203597524652155</v>
+        <v>-2.203597524652127</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.420769780650947</v>
+        <v>-2.420769780650946</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765827</v>
+        <v>0.08786371902765802</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.465756164808396e-05</v>
+        <v>6.4657561648084e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374641</v>
+        <v>0.0009969273959374665</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999521139866</v>
+        <v>0.1209999521140146</v>
       </c>
     </row>
     <row r="6">
@@ -1479,25 +1479,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.900967072018864</v>
+        <v>-2.900967072018792</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.058935913368399</v>
+        <v>-3.058935913368315</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431359</v>
+        <v>0.02921941151431353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006913950708356127</v>
+        <v>0.006913950708356131</v>
       </c>
       <c r="H6" t="n">
         <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971271</v>
+        <v>0.0007825190314971269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999358415974</v>
+        <v>0.1209999358415859</v>
       </c>
     </row>
     <row r="7">
@@ -1515,25 +1515,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.433445380976883</v>
+        <v>-3.433445380976915</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.55225002362041</v>
+        <v>-3.552250023620412</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799044</v>
+        <v>-0.009541766337799015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752079</v>
+        <v>0.006680214285752085</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289991e-05</v>
+        <v>4.620437260289981e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000620066753492464</v>
+        <v>0.0006200667534924634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999235694781</v>
+        <v>0.1209999235694483</v>
       </c>
     </row>
     <row r="8">
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.549789716013659</v>
+        <v>-3.549789716013629</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.661277902916882</v>
+        <v>-3.661277902916914</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178204</v>
+        <v>-0.01676581279178216</v>
       </c>
       <c r="G8" t="n">
         <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.469918633914963e-05</v>
+        <v>4.469918633914951e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747337</v>
+        <v>0.0005803385990747353</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999209197448</v>
+        <v>0.1209999209198065</v>
       </c>
     </row>
     <row r="9">
@@ -1587,25 +1587,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.263700982267203</v>
+        <v>-2.263700982267337</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.472845356318112</v>
+        <v>-2.472845356317956</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736005</v>
+        <v>0.07989090427360057</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294438</v>
+        <v>0.00721235424329444</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791398e-05</v>
+        <v>6.116855081791406e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750874</v>
+        <v>0.0009799963456750887</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999506375214</v>
+        <v>0.1209999506372319</v>
       </c>
     </row>
     <row r="10">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.975674700511282</v>
+        <v>-2.975674700511276</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.130577660942113</v>
+        <v>-3.13057766094211</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02618475354304766</v>
+        <v>0.02618475354304757</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699891</v>
+        <v>0.006898886718699889</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931317e-05</v>
+        <v>5.252414845931323e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801689</v>
+        <v>0.0007668618399801692</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999341806438</v>
+        <v>0.1209999341806465</v>
       </c>
     </row>
     <row r="11">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.369108114860852</v>
+        <v>-3.369108114860876</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.490548763184747</v>
+        <v>-3.49054876318475</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.00696080197853775</v>
+        <v>-0.006960801978537704</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006709262029071818</v>
+        <v>0.006709262029071785</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740441e-05</v>
+        <v>4.717660518740447e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199601</v>
+        <v>0.0006450866694199596</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999249987539</v>
+        <v>0.120999924998733</v>
       </c>
     </row>
   </sheetData>
@@ -1756,25 +1756,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.294689107117994</v>
+        <v>-1.294689107117985</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.52470062232917</v>
+        <v>-1.524700622329166</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1005026380413199</v>
+        <v>0.1005026380413198</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007350774813729365</v>
+        <v>0.007350774813729363</v>
       </c>
       <c r="H2" t="n">
-        <v>6.571721692417115e-05</v>
+        <v>6.571721692417118e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001092413434965748</v>
+        <v>0.001092413434965749</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999717042369</v>
+        <v>0.1209999717042423</v>
       </c>
     </row>
     <row r="3">
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.594285533042652</v>
+        <v>-1.594285533042685</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.820087119731961</v>
+        <v>-1.820087119731938</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09636540113066852</v>
+        <v>0.09636540113066856</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007312726439967746</v>
+        <v>0.007312726439967809</v>
       </c>
       <c r="H3" t="n">
-        <v>6.385850907915017e-05</v>
+        <v>6.385850907915014e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001059635361837415</v>
+        <v>0.001059635361837416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999652477565</v>
+        <v>0.1209999652477005</v>
       </c>
     </row>
     <row r="4">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.781553520690094</v>
+        <v>-1.781553520690176</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.005208024680584</v>
+        <v>-2.005208024680608</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09427285602063984</v>
+        <v>0.09427285602063995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007288038605682941</v>
+        <v>0.007288038605682944</v>
       </c>
       <c r="H4" t="n">
-        <v>6.399694265418645e-05</v>
+        <v>6.399694265418654e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001029651197070435</v>
+        <v>0.001029651197070432</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999612244426</v>
+        <v>0.1209999612243851</v>
       </c>
     </row>
     <row r="5">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.899123282443093</v>
+        <v>-1.899123282443168</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.116295544897085</v>
+        <v>-2.116295544897091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786371902765827</v>
+        <v>0.08786371902765802</v>
       </c>
       <c r="G5" t="n">
         <v>0.007246999899560616</v>
       </c>
       <c r="H5" t="n">
-        <v>6.465756164808396e-05</v>
+        <v>6.4657561648084e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009969273959374641</v>
+        <v>0.0009969273959374665</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999585691874</v>
+        <v>0.1209999585691188</v>
       </c>
     </row>
     <row r="6">
@@ -1900,25 +1900,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.625527686213487</v>
+        <v>-2.625527686213466</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.783496533402669</v>
+        <v>-2.78349653340265</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02921941151431359</v>
+        <v>0.02921941151431353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006913950708356127</v>
+        <v>0.006913950708356131</v>
       </c>
       <c r="H6" t="n">
         <v>5.302425377075151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007825190314971271</v>
+        <v>0.0007825190314971269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999416812444</v>
+        <v>0.1209999416812471</v>
       </c>
     </row>
     <row r="7">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.275962258504333</v>
+        <v>-3.275962258504337</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.394766904486695</v>
+        <v>-3.394766904486712</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009541766337799044</v>
+        <v>-0.009541766337799015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006680214285752079</v>
+        <v>0.006680214285752085</v>
       </c>
       <c r="H7" t="n">
-        <v>4.620437260289991e-05</v>
+        <v>4.620437260289981e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000620066753492464</v>
+        <v>0.0006200667534924634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999269083131</v>
+        <v>0.1209999269083264</v>
       </c>
     </row>
     <row r="8">
@@ -1972,25 +1972,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.413354992402458</v>
+        <v>-3.413354992402502</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.524843182198278</v>
+        <v>-3.524843182198338</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01676581279178204</v>
+        <v>-0.01676581279178216</v>
       </c>
       <c r="G8" t="n">
         <v>0.006629040989846974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.469918633914963e-05</v>
+        <v>4.469918633914951e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005803385990747337</v>
+        <v>0.0005803385990747353</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999238123411</v>
+        <v>0.120999923812358</v>
       </c>
     </row>
     <row r="9">
@@ -2008,25 +2008,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.869044331379985</v>
+        <v>-1.869044331379888</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.078188713798014</v>
+        <v>-2.078188713797886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0798909042736005</v>
+        <v>0.07989090427360057</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007212354243294438</v>
+        <v>0.00721235424329444</v>
       </c>
       <c r="H9" t="n">
-        <v>6.116855081791398e-05</v>
+        <v>6.116855081791406e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009799963456750874</v>
+        <v>0.0009799963456750887</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999590046402</v>
+        <v>0.1209999590046107</v>
       </c>
     </row>
     <row r="10">
@@ -2044,25 +2044,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.755477427594946</v>
+        <v>-2.755477427594948</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.910380392694229</v>
+        <v>-2.91038039269422</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02618475354304766</v>
+        <v>0.02618475354304757</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006898886718699891</v>
+        <v>0.006898886718699889</v>
       </c>
       <c r="H10" t="n">
-        <v>5.252414845931317e-05</v>
+        <v>5.252414845931323e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007668618399801689</v>
+        <v>0.0007668618399801692</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999388490952</v>
+        <v>0.1209999388490846</v>
       </c>
     </row>
     <row r="11">
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.228818386639041</v>
+        <v>-3.228818386639044</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3502590379372</v>
+        <v>-3.35025903793724</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.00696080197853775</v>
+        <v>-0.006960801978537704</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006709262029071818</v>
+        <v>0.006709262029071785</v>
       </c>
       <c r="H11" t="n">
-        <v>4.717660518740441e-05</v>
+        <v>4.717660518740447e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006450866694199601</v>
+        <v>0.0006450866694199596</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1209999279730183</v>
+        <v>0.1209999279730543</v>
       </c>
     </row>
   </sheetData>
